--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,736 +413,927 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Distance 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Distance 2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Angle</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Area</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fiducial 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>123.00925</v>
+      </c>
+      <c r="D2" t="n">
+        <v>85.94243</v>
+      </c>
+      <c r="E2" t="n">
+        <v>90.87862</v>
+      </c>
+      <c r="F2" t="n">
+        <v>506.13289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.44162</v>
+        <v>124.22356</v>
       </c>
       <c r="D3" t="n">
-        <v>16.30826</v>
+        <v>86.55871</v>
       </c>
       <c r="E3" t="n">
-        <v>16.74611</v>
+        <v>92.44607000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>42.60628</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.8445</v>
+        <v>510.44448</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.45369</v>
+        <v>122.22476</v>
       </c>
       <c r="D4" t="n">
-        <v>16.59922</v>
+        <v>86.62949999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>16.73236</v>
+        <v>90.64767999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>41.28175</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.04917</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.8194</v>
+        <v>505.56984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.79033</v>
+        <v>121.23017</v>
       </c>
       <c r="D5" t="n">
-        <v>16.6896</v>
+        <v>87.98291999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>16.73056</v>
+        <v>90.35669</v>
       </c>
       <c r="F5" t="n">
-        <v>42.60851</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.05086</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.78551</v>
+        <v>513.09568</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.02414</v>
+        <v>120.59894</v>
       </c>
       <c r="D6" t="n">
-        <v>16.55797</v>
+        <v>85.99907</v>
       </c>
       <c r="E6" t="n">
-        <v>16.59773</v>
+        <v>91.44216</v>
       </c>
       <c r="F6" t="n">
-        <v>42.67858</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05012</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.78572</v>
+        <v>520.76738</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.8423</v>
+        <v>122.38111</v>
       </c>
       <c r="D7" t="n">
-        <v>16.69901</v>
+        <v>88.83261</v>
       </c>
       <c r="E7" t="n">
-        <v>16.14252</v>
+        <v>91.73564</v>
       </c>
       <c r="F7" t="n">
-        <v>42.98582</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.04919</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.82541</v>
+        <v>515.3402599999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.04364</v>
+        <v>122.64114</v>
       </c>
       <c r="D8" t="n">
-        <v>16.83773</v>
+        <v>85.37979</v>
       </c>
       <c r="E8" t="n">
-        <v>16.36425</v>
+        <v>89.37696</v>
       </c>
       <c r="F8" t="n">
-        <v>42.03395</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.05061</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.83569</v>
+        <v>521.91246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.72289</v>
+        <v>118.37123</v>
       </c>
       <c r="D9" t="n">
-        <v>16.41232</v>
+        <v>85.30016000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>16.95184</v>
+        <v>89.53449999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>42.84563</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.86102</v>
+        <v>513.93611</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.86843</v>
+        <v>119.5354</v>
       </c>
       <c r="D10" t="n">
-        <v>16.77169</v>
+        <v>87.25226000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>16.50505</v>
+        <v>91.61758</v>
       </c>
       <c r="F10" t="n">
-        <v>41.96326</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.80463</v>
+        <v>514.92367</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.73142</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.5713</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.80133</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.04954</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05139</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.82042</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Micro Bump 3</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8.851789999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24.08706</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60451</v>
+        <v>8.7042</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10837</v>
+        <v>24.43926</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60944</v>
+        <v>8.65545</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09791</v>
+        <v>24.48484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.61772</v>
+        <v>8.55368</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13006</v>
+        <v>24.50662</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60316</v>
+        <v>8.46482</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10166</v>
+        <v>24.46056</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60309</v>
+        <v>8.363390000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10977</v>
+        <v>24.76492</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60185</v>
+        <v>8.599970000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11547</v>
+        <v>24.48679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60783</v>
+        <v>8.773860000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11667</v>
+        <v>24.83391</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.6042</v>
+        <v>8.69237</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11033</v>
+        <v>24.7827</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.60061</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.11439</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17.11025</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.22331</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.46864</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42.89126</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.04986</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.85634</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.7556</v>
+        <v>16.70965</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08021</v>
+        <v>16.43793</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6089599999999999</v>
+        <v>16.57616</v>
       </c>
       <c r="F23" t="n">
-        <v>0.96213</v>
+        <v>42.87566</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10982</v>
+        <v>0.05091</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09247</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12691</v>
+        <v>1.82221</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75095</v>
+        <v>16.98968</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08176</v>
+        <v>16.65241</v>
       </c>
       <c r="E24" t="n">
-        <v>0.60584</v>
+        <v>16.77736</v>
       </c>
       <c r="F24" t="n">
-        <v>0.96941</v>
+        <v>41.79646</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10836</v>
+        <v>0.05037</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00752</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09155000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12752</v>
+        <v>1.8221</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.72599</v>
+        <v>16.72826</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0803</v>
+        <v>16.46978</v>
       </c>
       <c r="E25" t="n">
-        <v>0.61924</v>
+        <v>16.55215</v>
       </c>
       <c r="F25" t="n">
-        <v>0.96622</v>
+        <v>42.25398</v>
       </c>
       <c r="G25" t="n">
-        <v>0.11156</v>
+        <v>0.05169</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09252000000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12779</v>
+        <v>1.81693</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7425</v>
+        <v>16.82627</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08035</v>
+        <v>16.43614</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60539</v>
+        <v>16.66121</v>
       </c>
       <c r="F26" t="n">
-        <v>0.94101</v>
+        <v>41.66479</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10785</v>
+        <v>0.05066</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09529</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12627</v>
+        <v>1.80006</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.74765</v>
+        <v>16.94392</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07928</v>
+        <v>16.7651</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60553</v>
+        <v>16.78019</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95284</v>
+        <v>42.76477</v>
       </c>
       <c r="G27" t="n">
-        <v>0.11183</v>
+        <v>0.05108</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09421</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.126</v>
+        <v>1.79299</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74574</v>
+        <v>16.625</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07986</v>
+        <v>16.2676</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6055</v>
+        <v>16.60074</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96023</v>
+        <v>43.11405</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1117</v>
+        <v>0.05077</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09379999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12564</v>
+        <v>1.82595</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7656500000000001</v>
+        <v>16.86872</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08085000000000001</v>
+        <v>16.70996</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60368</v>
+        <v>16.81463</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9668</v>
+        <v>42.75706</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10938</v>
+        <v>0.05097</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00751</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09284000000000001</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12484</v>
+        <v>1.80864</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.73122</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.48208</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.61754</v>
+      </c>
+      <c r="F30" t="n">
+        <v>42.85714</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.7969</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.75251</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.59473</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.96441</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10782</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09286</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12593</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.75281</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08178000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.61088</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.95669</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10683</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09234000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12926</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.75424</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.60526</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9706399999999999</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11079</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09203</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1262</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.07937</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.59156</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.94052</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10881</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09205000000000001</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12766</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.74364</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08098</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6117899999999999</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9771300000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.11069</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00744</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09503</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12736</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7532799999999999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08089</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.59965</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.96355</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.10691</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09447999999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12731</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.74552</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08248999999999999</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6091800000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.97261</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.10902</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09284000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12776</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.73937</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.07957</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.61053</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.95722</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10964</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09343</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12395</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="C39" t="n">
+        <v>0.73812</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.07902000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6029</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.97355</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10863</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00741</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09331</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12693</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>0.75227</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08241999999999999</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.60743</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.95291</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.10916</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00737</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09050999999999999</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.124</v>
+      <c r="C40" t="n">
+        <v>0.7331800000000001</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08007</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.61047</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.95112</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11054</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00747</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09265</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12862</v>
       </c>
     </row>
   </sheetData>
